--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -55790,7 +55790,7 @@
       </c>
       <c r="G791" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H791" s="5" t="n">
@@ -55852,7 +55852,7 @@
       </c>
       <c r="G792" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H792" s="5" t="n">
@@ -56636,7 +56636,7 @@
       </c>
       <c r="G804" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H804" s="5" t="n">
@@ -56698,7 +56698,7 @@
       </c>
       <c r="G805" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H805" s="5" t="n">
@@ -56760,7 +56760,7 @@
       </c>
       <c r="G806" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H806" s="5" t="n">
@@ -56822,7 +56822,7 @@
       </c>
       <c r="G807" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H807" s="5" t="n">
@@ -56884,7 +56884,7 @@
       </c>
       <c r="G808" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H808" s="5" t="n">
@@ -56946,7 +56946,7 @@
       </c>
       <c r="G809" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H809" s="5" t="n">
@@ -57358,7 +57358,7 @@
       </c>
       <c r="G815" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H815" s="5" t="n">
@@ -57420,7 +57420,7 @@
       </c>
       <c r="G816" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H816" s="5" t="n">
@@ -57482,7 +57482,7 @@
       </c>
       <c r="G817" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H817" s="5" t="n">
@@ -57544,7 +57544,7 @@
       </c>
       <c r="G818" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H818" s="5" t="n">
@@ -57606,7 +57606,7 @@
       </c>
       <c r="G819" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H819" s="5" t="n">
@@ -57668,7 +57668,7 @@
       </c>
       <c r="G820" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H820" s="5" t="n">
@@ -57730,7 +57730,7 @@
       </c>
       <c r="G821" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H821" s="5" t="n">
@@ -57792,7 +57792,7 @@
       </c>
       <c r="G822" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H822" s="5" t="n">
@@ -58204,7 +58204,7 @@
       </c>
       <c r="G828" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H828" s="5" t="n">
@@ -58266,7 +58266,7 @@
       </c>
       <c r="G829" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H829" s="5" t="n">
@@ -58328,7 +58328,7 @@
       </c>
       <c r="G830" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H830" s="5" t="n">
@@ -58390,7 +58390,7 @@
       </c>
       <c r="G831" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H831" s="5" t="n">
@@ -58452,7 +58452,7 @@
       </c>
       <c r="G832" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H832" s="5" t="n">
@@ -58514,7 +58514,7 @@
       </c>
       <c r="G833" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H833" s="5" t="n">
@@ -58576,7 +58576,7 @@
       </c>
       <c r="G834" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H834" s="5" t="n">
@@ -58638,7 +58638,7 @@
       </c>
       <c r="G835" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H835" s="5" t="n">
@@ -59050,7 +59050,7 @@
       </c>
       <c r="G841" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H841" s="5" t="n">
@@ -59112,7 +59112,7 @@
       </c>
       <c r="G842" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H842" s="5" t="n">
@@ -59174,7 +59174,7 @@
       </c>
       <c r="G843" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H843" s="5" t="n">
@@ -59236,7 +59236,7 @@
       </c>
       <c r="G844" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H844" s="5" t="n">
@@ -59298,7 +59298,7 @@
       </c>
       <c r="G845" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H845" s="5" t="n">
@@ -59360,7 +59360,7 @@
       </c>
       <c r="G846" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H846" s="5" t="n">
@@ -59422,7 +59422,7 @@
       </c>
       <c r="G847" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H847" s="5" t="n">
@@ -59484,7 +59484,7 @@
       </c>
       <c r="G848" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H848" s="5" t="n">
@@ -59896,7 +59896,7 @@
       </c>
       <c r="G854" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H854" s="5" t="n">
@@ -59958,7 +59958,7 @@
       </c>
       <c r="G855" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H855" s="5" t="n">
@@ -60020,7 +60020,7 @@
       </c>
       <c r="G856" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H856" s="5" t="n">
@@ -60082,7 +60082,7 @@
       </c>
       <c r="G857" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H857" s="5" t="n">
@@ -60144,7 +60144,7 @@
       </c>
       <c r="G858" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H858" s="5" t="n">
@@ -60206,7 +60206,7 @@
       </c>
       <c r="G859" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H859" s="5" t="n">
@@ -60268,7 +60268,7 @@
       </c>
       <c r="G860" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H860" s="5" t="n">
@@ -60330,7 +60330,7 @@
       </c>
       <c r="G861" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H861" s="5" t="n">
@@ -60392,7 +60392,7 @@
       </c>
       <c r="G862" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H862" s="5" t="n">
@@ -60454,7 +60454,7 @@
       </c>
       <c r="G863" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H863" s="5" t="n">
@@ -60516,7 +60516,7 @@
       </c>
       <c r="G864" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H864" s="5" t="n">
@@ -60578,7 +60578,7 @@
       </c>
       <c r="G865" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H865" s="5" t="n">
@@ -60640,7 +60640,7 @@
       </c>
       <c r="G866" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H866" s="5" t="n">
@@ -60702,7 +60702,7 @@
       </c>
       <c r="G867" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H867" s="5" t="n">
@@ -60764,7 +60764,7 @@
       </c>
       <c r="G868" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H868" s="5" t="n">
@@ -60826,7 +60826,7 @@
       </c>
       <c r="G869" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H869" s="5" t="n">
@@ -60888,7 +60888,7 @@
       </c>
       <c r="G870" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H870" s="5" t="n">
@@ -60950,7 +60950,7 @@
       </c>
       <c r="G871" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H871" s="5" t="n">
@@ -61012,7 +61012,7 @@
       </c>
       <c r="G872" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H872" s="5" t="n">
@@ -61074,7 +61074,7 @@
       </c>
       <c r="G873" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H873" s="5" t="n">
@@ -61136,7 +61136,7 @@
       </c>
       <c r="G874" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H874" s="5" t="n">
@@ -61198,7 +61198,7 @@
       </c>
       <c r="G875" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H875" s="5" t="n">
@@ -61322,7 +61322,7 @@
       </c>
       <c r="G877" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H877" s="5" t="n">
@@ -61384,7 +61384,7 @@
       </c>
       <c r="G878" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H878" s="5" t="n">
@@ -61446,7 +61446,7 @@
       </c>
       <c r="G879" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H879" s="5" t="n">
@@ -61508,7 +61508,7 @@
       </c>
       <c r="G880" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H880" s="5" t="n">
@@ -61570,7 +61570,7 @@
       </c>
       <c r="G881" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H881" s="5" t="n">
@@ -61632,7 +61632,7 @@
       </c>
       <c r="G882" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H882" s="5" t="n">
@@ -61694,7 +61694,7 @@
       </c>
       <c r="G883" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H883" s="5" t="n">
@@ -61756,7 +61756,7 @@
       </c>
       <c r="G884" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H884" s="5" t="n">
@@ -61818,7 +61818,7 @@
       </c>
       <c r="G885" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H885" s="5" t="n">
@@ -61880,7 +61880,7 @@
       </c>
       <c r="G886" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H886" s="5" t="n">
@@ -61942,7 +61942,7 @@
       </c>
       <c r="G887" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H887" s="5" t="n">
@@ -62144,7 +62144,7 @@
       </c>
       <c r="G890" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H890" s="5" t="n">
@@ -62346,7 +62346,7 @@
       </c>
       <c r="G893" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H893" s="5" t="n">
@@ -62408,7 +62408,7 @@
       </c>
       <c r="G894" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H894" s="5" t="n">
@@ -62470,7 +62470,7 @@
       </c>
       <c r="G895" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H895" s="5" t="n">
@@ -62532,7 +62532,7 @@
       </c>
       <c r="G896" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H896" s="5" t="n">
@@ -62594,7 +62594,7 @@
       </c>
       <c r="G897" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H897" s="5" t="n">
@@ -62656,7 +62656,7 @@
       </c>
       <c r="G898" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H898" s="5" t="n">
@@ -62718,7 +62718,7 @@
       </c>
       <c r="G899" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H899" s="5" t="n">
@@ -62780,7 +62780,7 @@
       </c>
       <c r="G900" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H900" s="5" t="n">
@@ -62982,7 +62982,7 @@
       </c>
       <c r="G903" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H903" s="5" t="n">
@@ -63114,7 +63114,7 @@
       </c>
       <c r="G905" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H905" s="5" t="n">
@@ -63176,7 +63176,7 @@
       </c>
       <c r="G906" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H906" s="5" t="n">
@@ -63238,7 +63238,7 @@
       </c>
       <c r="G907" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H907" s="5" t="n">
@@ -63300,7 +63300,7 @@
       </c>
       <c r="G908" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H908" s="5" t="n">
@@ -63362,7 +63362,7 @@
       </c>
       <c r="G909" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H909" s="5" t="n">
@@ -63424,7 +63424,7 @@
       </c>
       <c r="G910" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H910" s="5" t="n">
@@ -63486,7 +63486,7 @@
       </c>
       <c r="G911" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H911" s="5" t="n">
@@ -63548,7 +63548,7 @@
       </c>
       <c r="G912" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H912" s="5" t="n">
@@ -63610,7 +63610,7 @@
       </c>
       <c r="G913" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H913" s="5" t="n">
@@ -63672,7 +63672,7 @@
       </c>
       <c r="G914" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H914" s="5" t="n">
@@ -63734,7 +63734,7 @@
       </c>
       <c r="G915" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H915" s="5" t="n">
@@ -63796,7 +63796,7 @@
       </c>
       <c r="G916" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H916" s="5" t="n">
@@ -63858,7 +63858,7 @@
       </c>
       <c r="G917" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H917" s="5" t="n">
@@ -63920,7 +63920,7 @@
       </c>
       <c r="G918" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H918" s="5" t="n">
@@ -63982,7 +63982,7 @@
       </c>
       <c r="G919" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H919" s="5" t="n">
@@ -64044,7 +64044,7 @@
       </c>
       <c r="G920" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H920" s="5" t="n">
@@ -64106,7 +64106,7 @@
       </c>
       <c r="G921" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H921" s="5" t="n">
@@ -64168,7 +64168,7 @@
       </c>
       <c r="G922" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H922" s="5" t="n">
@@ -64230,7 +64230,7 @@
       </c>
       <c r="G923" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H923" s="5" t="n">
@@ -64292,7 +64292,7 @@
       </c>
       <c r="G924" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H924" s="5" t="n">
@@ -64354,7 +64354,7 @@
       </c>
       <c r="G925" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H925" s="5" t="n">
@@ -64416,7 +64416,7 @@
       </c>
       <c r="G926" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H926" s="5" t="n">
@@ -64478,7 +64478,7 @@
       </c>
       <c r="G927" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H927" s="5" t="n">
@@ -64540,7 +64540,7 @@
       </c>
       <c r="G928" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H928" s="5" t="n">
@@ -64602,7 +64602,7 @@
       </c>
       <c r="G929" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H929" s="5" t="n">
@@ -64664,7 +64664,7 @@
       </c>
       <c r="G930" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H930" s="5" t="n">
@@ -64726,7 +64726,7 @@
       </c>
       <c r="G931" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H931" s="5" t="n">
@@ -64788,7 +64788,7 @@
       </c>
       <c r="G932" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H932" s="5" t="n">
@@ -64850,7 +64850,7 @@
       </c>
       <c r="G933" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H933" s="5" t="n">
@@ -64912,7 +64912,7 @@
       </c>
       <c r="G934" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H934" s="5" t="n">
@@ -64974,7 +64974,7 @@
       </c>
       <c r="G935" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H935" s="5" t="n">
@@ -65036,7 +65036,7 @@
       </c>
       <c r="G936" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H936" s="5" t="n">
@@ -65098,7 +65098,7 @@
       </c>
       <c r="G937" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H937" s="5" t="n">
@@ -65160,7 +65160,7 @@
       </c>
       <c r="G938" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H938" s="5" t="n">
@@ -65222,7 +65222,7 @@
       </c>
       <c r="G939" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H939" s="5" t="n">
@@ -65284,7 +65284,7 @@
       </c>
       <c r="G940" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H940" s="5" t="n">
@@ -65346,7 +65346,7 @@
       </c>
       <c r="G941" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H941" s="5" t="n">
@@ -65408,7 +65408,7 @@
       </c>
       <c r="G942" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H942" s="5" t="n">
@@ -65470,7 +65470,7 @@
       </c>
       <c r="G943" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H943" s="5" t="n">
@@ -65532,7 +65532,7 @@
       </c>
       <c r="G944" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H944" s="5" t="n">
@@ -65594,7 +65594,7 @@
       </c>
       <c r="G945" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H945" s="5" t="n">
@@ -65656,7 +65656,7 @@
       </c>
       <c r="G946" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H946" s="5" t="n">
@@ -65718,7 +65718,7 @@
       </c>
       <c r="G947" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H947" s="5" t="n">
@@ -65780,7 +65780,7 @@
       </c>
       <c r="G948" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H948" s="5" t="n">
@@ -65842,7 +65842,7 @@
       </c>
       <c r="G949" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H949" s="5" t="n">
@@ -65904,7 +65904,7 @@
       </c>
       <c r="G950" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H950" s="5" t="n">
@@ -65966,7 +65966,7 @@
       </c>
       <c r="G951" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H951" s="5" t="n">
@@ -66028,7 +66028,7 @@
       </c>
       <c r="G952" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H952" s="5" t="n">
@@ -66090,7 +66090,7 @@
       </c>
       <c r="G953" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H953" s="5" t="n">
@@ -66152,7 +66152,7 @@
       </c>
       <c r="G954" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H954" s="5" t="n">
@@ -66214,7 +66214,7 @@
       </c>
       <c r="G955" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H955" s="5" t="n">
@@ -66276,7 +66276,7 @@
       </c>
       <c r="G956" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H956" s="5" t="n">
@@ -66338,7 +66338,7 @@
       </c>
       <c r="G957" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H957" s="5" t="n">
@@ -66400,7 +66400,7 @@
       </c>
       <c r="G958" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H958" s="5" t="n">
@@ -66462,7 +66462,7 @@
       </c>
       <c r="G959" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H959" s="5" t="n">
@@ -66524,7 +66524,7 @@
       </c>
       <c r="G960" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H960" s="5" t="n">
@@ -66586,7 +66586,7 @@
       </c>
       <c r="G961" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H961" s="5" t="n">
@@ -66648,7 +66648,7 @@
       </c>
       <c r="G962" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H962" s="5" t="n">
@@ -66710,7 +66710,7 @@
       </c>
       <c r="G963" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H963" s="5" t="n">
@@ -66772,7 +66772,7 @@
       </c>
       <c r="G964" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H964" s="5" t="n">
@@ -66834,7 +66834,7 @@
       </c>
       <c r="G965" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H965" s="5" t="n">
@@ -67246,7 +67246,7 @@
       </c>
       <c r="G971" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H971" s="5" t="n">
@@ -67308,7 +67308,7 @@
       </c>
       <c r="G972" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H972" s="5" t="n">
@@ -67370,7 +67370,7 @@
       </c>
       <c r="G973" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H973" s="5" t="n">
@@ -67432,7 +67432,7 @@
       </c>
       <c r="G974" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H974" s="5" t="n">
@@ -67494,7 +67494,7 @@
       </c>
       <c r="G975" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H975" s="5" t="n">
@@ -67556,7 +67556,7 @@
       </c>
       <c r="G976" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H976" s="5" t="n">
@@ -67618,7 +67618,7 @@
       </c>
       <c r="G977" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H977" s="5" t="n">
@@ -67680,7 +67680,7 @@
       </c>
       <c r="G978" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H978" s="5" t="n">
@@ -67742,7 +67742,7 @@
       </c>
       <c r="G979" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H979" s="5" t="n">
@@ -67804,7 +67804,7 @@
       </c>
       <c r="G980" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H980" s="5" t="n">
@@ -67866,7 +67866,7 @@
       </c>
       <c r="G981" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H981" s="5" t="n">
@@ -67928,7 +67928,7 @@
       </c>
       <c r="G982" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H982" s="5" t="n">
@@ -67990,7 +67990,7 @@
       </c>
       <c r="G983" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H983" s="5" t="n">
@@ -68052,7 +68052,7 @@
       </c>
       <c r="G984" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H984" s="5" t="n">
@@ -68114,7 +68114,7 @@
       </c>
       <c r="G985" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H985" s="5" t="n">
@@ -68176,7 +68176,7 @@
       </c>
       <c r="G986" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H986" s="5" t="n">
@@ -68238,7 +68238,7 @@
       </c>
       <c r="G987" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H987" s="5" t="n">
@@ -68300,7 +68300,7 @@
       </c>
       <c r="G988" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H988" s="5" t="n">
@@ -68362,7 +68362,7 @@
       </c>
       <c r="G989" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H989" s="5" t="n">
@@ -68424,7 +68424,7 @@
       </c>
       <c r="G990" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H990" s="5" t="n">
@@ -68486,7 +68486,7 @@
       </c>
       <c r="G991" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H991" s="5" t="n">
@@ -68548,7 +68548,7 @@
       </c>
       <c r="G992" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H992" s="5" t="n">
@@ -68610,7 +68610,7 @@
       </c>
       <c r="G993" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H993" s="5" t="n">
@@ -68672,7 +68672,7 @@
       </c>
       <c r="G994" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H994" s="5" t="n">
@@ -68734,7 +68734,7 @@
       </c>
       <c r="G995" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H995" s="5" t="n">
@@ -68796,7 +68796,7 @@
       </c>
       <c r="G996" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H996" s="5" t="n">
@@ -68858,7 +68858,7 @@
       </c>
       <c r="G997" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H997" s="5" t="n">
@@ -68920,7 +68920,7 @@
       </c>
       <c r="G998" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H998" s="5" t="n">
@@ -68982,7 +68982,7 @@
       </c>
       <c r="G999" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H999" s="5" t="n">
@@ -69044,7 +69044,7 @@
       </c>
       <c r="G1000" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1000" s="5" t="n">
@@ -69106,7 +69106,7 @@
       </c>
       <c r="G1001" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1001" s="5" t="n">
@@ -69168,7 +69168,7 @@
       </c>
       <c r="G1002" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H1002" s="5" t="n">
@@ -69230,7 +69230,7 @@
       </c>
       <c r="G1003" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1003" s="5" t="n">
@@ -69292,7 +69292,7 @@
       </c>
       <c r="G1004" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1004" s="5" t="n">
@@ -69424,7 +69424,7 @@
       </c>
       <c r="G1006" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1006" s="5" t="n">
@@ -69486,7 +69486,7 @@
       </c>
       <c r="G1007" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H1007" s="5" t="n">
@@ -69548,7 +69548,7 @@
       </c>
       <c r="G1008" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H1008" s="5" t="n">
@@ -69610,7 +69610,7 @@
       </c>
       <c r="G1009" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1009" s="5" t="n">
@@ -69672,7 +69672,7 @@
       </c>
       <c r="G1010" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1010" s="5" t="n">
@@ -69734,7 +69734,7 @@
       </c>
       <c r="G1011" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1011" s="5" t="n">
@@ -69796,7 +69796,7 @@
       </c>
       <c r="G1012" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1012" s="5" t="n">
@@ -69858,7 +69858,7 @@
       </c>
       <c r="G1013" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1013" s="5" t="n">
@@ -69920,7 +69920,7 @@
       </c>
       <c r="G1014" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1014" s="5" t="n">
@@ -69982,7 +69982,7 @@
       </c>
       <c r="G1015" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1015" s="5" t="n">
@@ -70044,7 +70044,7 @@
       </c>
       <c r="G1016" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1016" s="5" t="n">
@@ -70106,7 +70106,7 @@
       </c>
       <c r="G1017" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1017" s="5" t="n">
@@ -70168,7 +70168,7 @@
       </c>
       <c r="G1018" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1018" s="5" t="n">
@@ -70230,7 +70230,7 @@
       </c>
       <c r="G1019" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1019" s="5" t="n">
@@ -70292,7 +70292,7 @@
       </c>
       <c r="G1020" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H1020" s="5" t="n">
@@ -70354,7 +70354,7 @@
       </c>
       <c r="G1021" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1021" s="5" t="n">
@@ -70416,7 +70416,7 @@
       </c>
       <c r="G1022" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1022" s="5" t="n">
@@ -70478,7 +70478,7 @@
       </c>
       <c r="G1023" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H1023" s="5" t="n">
@@ -70540,7 +70540,7 @@
       </c>
       <c r="G1024" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H1024" s="5" t="n">
@@ -70602,7 +70602,7 @@
       </c>
       <c r="G1025" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H1025" s="5" t="n">
@@ -70664,7 +70664,7 @@
       </c>
       <c r="G1026" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H1026" s="5" t="n">
@@ -70726,7 +70726,7 @@
       </c>
       <c r="G1027" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H1027" s="5" t="n">
@@ -70788,7 +70788,7 @@
       </c>
       <c r="G1028" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1028" s="5" t="n">
@@ -70850,7 +70850,7 @@
       </c>
       <c r="G1029" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1029" s="5" t="n">
@@ -70912,7 +70912,7 @@
       </c>
       <c r="G1030" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H1030" s="5" t="n">
@@ -70974,7 +70974,7 @@
       </c>
       <c r="G1031" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H1031" s="5" t="n">
@@ -71036,7 +71036,7 @@
       </c>
       <c r="G1032" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H1032" s="5" t="n">
@@ -71098,7 +71098,7 @@
       </c>
       <c r="G1033" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H1033" s="5" t="n">
@@ -71160,7 +71160,7 @@
       </c>
       <c r="G1034" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H1034" s="5" t="n">
@@ -71222,7 +71222,7 @@
       </c>
       <c r="G1035" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H1035" s="5" t="n">
@@ -71284,7 +71284,7 @@
       </c>
       <c r="G1036" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H1036" s="5" t="n">
@@ -71346,7 +71346,7 @@
       </c>
       <c r="G1037" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1037" s="5" t="n">
@@ -71408,7 +71408,7 @@
       </c>
       <c r="G1038" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H1038" s="5" t="n">
@@ -71470,7 +71470,7 @@
       </c>
       <c r="G1039" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H1039" s="5" t="n">
@@ -71532,7 +71532,7 @@
       </c>
       <c r="G1040" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H1040" s="5" t="n">
@@ -71594,7 +71594,7 @@
       </c>
       <c r="G1041" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H1041" s="5" t="n">
@@ -71656,7 +71656,7 @@
       </c>
       <c r="G1042" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H1042" s="5" t="n">
@@ -71718,7 +71718,7 @@
       </c>
       <c r="G1043" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H1043" s="5" t="n">
@@ -71920,7 +71920,7 @@
       </c>
       <c r="G1046" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H1046" s="5" t="n">
@@ -71982,7 +71982,7 @@
       </c>
       <c r="G1047" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H1047" s="5" t="n">
@@ -72044,7 +72044,7 @@
       </c>
       <c r="G1048" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H1048" s="5" t="n">
@@ -72106,7 +72106,7 @@
       </c>
       <c r="G1049" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H1049" s="5" t="n">
@@ -72168,7 +72168,7 @@
       </c>
       <c r="G1050" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1050" s="5" t="n">
@@ -72230,7 +72230,7 @@
       </c>
       <c r="G1051" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1051" s="5" t="n">
@@ -72292,7 +72292,7 @@
       </c>
       <c r="G1052" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H1052" s="5" t="n">
@@ -72354,7 +72354,7 @@
       </c>
       <c r="G1053" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1053" s="5" t="n">
@@ -72416,7 +72416,7 @@
       </c>
       <c r="G1054" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1054" s="5" t="n">
@@ -72478,7 +72478,7 @@
       </c>
       <c r="G1055" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1055" s="5" t="n">
@@ -72540,7 +72540,7 @@
       </c>
       <c r="G1056" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1056" s="5" t="n">
@@ -72602,7 +72602,7 @@
       </c>
       <c r="G1057" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H1057" s="5" t="n">
@@ -72664,7 +72664,7 @@
       </c>
       <c r="G1058" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H1058" s="5" t="n">
@@ -72726,7 +72726,7 @@
       </c>
       <c r="G1059" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1059" s="5" t="n">
@@ -72788,7 +72788,7 @@
       </c>
       <c r="G1060" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H1060" s="5" t="n">
@@ -72850,7 +72850,7 @@
       </c>
       <c r="G1061" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H1061" s="5" t="n">
@@ -72912,7 +72912,7 @@
       </c>
       <c r="G1062" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H1062" s="5" t="n">
@@ -72974,7 +72974,7 @@
       </c>
       <c r="G1063" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H1063" s="5" t="n">
@@ -73036,7 +73036,7 @@
       </c>
       <c r="G1064" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1064" s="5" t="n">
@@ -73098,7 +73098,7 @@
       </c>
       <c r="G1065" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1065" s="5" t="n">
@@ -73160,7 +73160,7 @@
       </c>
       <c r="G1066" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1066" s="5" t="n">
@@ -73222,7 +73222,7 @@
       </c>
       <c r="G1067" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1067" s="5" t="n">
@@ -73284,7 +73284,7 @@
       </c>
       <c r="G1068" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1068" s="5" t="n">
@@ -73346,7 +73346,7 @@
       </c>
       <c r="G1069" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1069" s="5" t="n">
@@ -73408,7 +73408,7 @@
       </c>
       <c r="G1070" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H1070" s="5" t="n">
@@ -73470,7 +73470,7 @@
       </c>
       <c r="G1071" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H1071" s="5" t="n">
@@ -73532,7 +73532,7 @@
       </c>
       <c r="G1072" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1072" s="5" t="n">
@@ -73594,7 +73594,7 @@
       </c>
       <c r="G1073" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H1073" s="5" t="n">
@@ -73656,7 +73656,7 @@
       </c>
       <c r="G1074" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H1074" s="5" t="n">
@@ -73718,7 +73718,7 @@
       </c>
       <c r="G1075" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H1075" s="5" t="n">
@@ -73780,7 +73780,7 @@
       </c>
       <c r="G1076" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1076" s="5" t="n">
@@ -73842,7 +73842,7 @@
       </c>
       <c r="G1077" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H1077" s="5" t="n">
@@ -73904,7 +73904,7 @@
       </c>
       <c r="G1078" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1078" s="5" t="n">
@@ -73966,7 +73966,7 @@
       </c>
       <c r="G1079" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1079" s="5" t="n">
@@ -74028,7 +74028,7 @@
       </c>
       <c r="G1080" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1080" s="5" t="n">
@@ -74090,7 +74090,7 @@
       </c>
       <c r="G1081" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H1081" s="5" t="n">
@@ -74152,7 +74152,7 @@
       </c>
       <c r="G1082" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H1082" s="5" t="n">
@@ -74284,7 +74284,7 @@
       </c>
       <c r="G1084" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1084" s="5" t="n">
@@ -74346,7 +74346,7 @@
       </c>
       <c r="G1085" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H1085" s="5" t="n">
@@ -74408,7 +74408,7 @@
       </c>
       <c r="G1086" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H1086" s="5" t="n">
@@ -74470,7 +74470,7 @@
       </c>
       <c r="G1087" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H1087" s="5" t="n">
@@ -74532,7 +74532,7 @@
       </c>
       <c r="G1088" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H1088" s="5" t="n">
@@ -74594,7 +74594,7 @@
       </c>
       <c r="G1089" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H1089" s="5" t="n">
@@ -74656,7 +74656,7 @@
       </c>
       <c r="G1090" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1090" s="5" t="n">
@@ -74718,7 +74718,7 @@
       </c>
       <c r="G1091" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1091" s="5" t="n">
@@ -74780,7 +74780,7 @@
       </c>
       <c r="G1092" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1092" s="5" t="n">
@@ -74842,7 +74842,7 @@
       </c>
       <c r="G1093" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H1093" s="5" t="n">
@@ -74904,7 +74904,7 @@
       </c>
       <c r="G1094" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1094" s="5" t="n">
@@ -74966,7 +74966,7 @@
       </c>
       <c r="G1095" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1095" s="5" t="n">
@@ -75028,7 +75028,7 @@
       </c>
       <c r="G1096" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1096" s="5" t="n">
@@ -75090,7 +75090,7 @@
       </c>
       <c r="G1097" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1097" s="5" t="n">
@@ -75152,7 +75152,7 @@
       </c>
       <c r="G1098" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H1098" s="5" t="n">
@@ -75354,7 +75354,7 @@
       </c>
       <c r="G1101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H1101" s="5" t="n">
@@ -75416,7 +75416,7 @@
       </c>
       <c r="G1102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H1102" s="5" t="n">
@@ -75478,7 +75478,7 @@
       </c>
       <c r="G1103" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H1103" s="5" t="n">
@@ -75540,7 +75540,7 @@
       </c>
       <c r="G1104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H1104" s="5" t="n">
@@ -75602,7 +75602,7 @@
       </c>
       <c r="G1105" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H1105" s="5" t="n">
@@ -75664,7 +75664,7 @@
       </c>
       <c r="G1106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1106" s="5" t="n">
@@ -75726,7 +75726,7 @@
       </c>
       <c r="G1107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1107" s="5" t="n">
@@ -75788,7 +75788,7 @@
       </c>
       <c r="G1108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H1108" s="5" t="n">
@@ -75850,7 +75850,7 @@
       </c>
       <c r="G1109" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H1109" s="5" t="n">
@@ -75912,7 +75912,7 @@
       </c>
       <c r="G1110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1110" s="5" t="n">
@@ -75974,7 +75974,7 @@
       </c>
       <c r="G1111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H1111" s="5" t="n">
@@ -76036,7 +76036,7 @@
       </c>
       <c r="G1112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H1112" s="5" t="n">
@@ -76098,7 +76098,7 @@
       </c>
       <c r="G1113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H1113" s="5" t="n">
@@ -76650,7 +76650,7 @@
       </c>
       <c r="G1121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H1121" s="5" t="n">
@@ -76712,7 +76712,7 @@
       </c>
       <c r="G1122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H1122" s="5" t="n">
@@ -84169,7 +84169,7 @@
           <t>K | 426呎 (2房)
 $1022万
 $24,002/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -84177,7 +84177,7 @@
           <t>L | 305呎 (1房)
 $732万
 $24,000/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -84248,7 +84248,7 @@
           <t>F | 307呎 (1房)
 $658万
 $21,417/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -84256,7 +84256,7 @@
           <t>G | 306呎 (1房)
 $658万
 $21,490/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -84264,7 +84264,7 @@
           <t>H | 306呎 (1房)
 $660万
 $21,556/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -84272,7 +84272,7 @@
           <t>J | 308呎 (1房)
 $664万
 $21,552/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr">
@@ -84280,7 +84280,7 @@
           <t>K | 426呎 (2房)
 $908万
 $21,319/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
@@ -84288,7 +84288,7 @@
           <t>L | 305呎 (1房)
 $679万
 $22,269/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -84359,7 +84359,7 @@
           <t>F | 307呎 (1房)
 $651万
 $21,205/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -84367,7 +84367,7 @@
           <t>G | 306呎 (1房)
 $651万
 $21,275/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -84375,7 +84375,7 @@
           <t>H | 306呎 (1房)
 $653万
 $21,346/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -84383,7 +84383,7 @@
           <t>J | 308呎 (1房)
 $658万
 $21,347/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
@@ -84391,7 +84391,7 @@
           <t>K | 426呎 (2房)
 $899万
 $21,108/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -84399,7 +84399,7 @@
           <t>L | 305呎 (1房)
 $672万
 $22,049/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr">
@@ -84407,7 +84407,7 @@
           <t>M | 429呎 (2房)
 $994万
 $23,166/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -84415,7 +84415,7 @@
           <t>N | 278呎 (1房)
 $664万
 $23,892/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -84470,7 +84470,7 @@
           <t>F | 307呎 (1房)
 $644万
 $20,993/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -84478,7 +84478,7 @@
           <t>G | 306呎 (1房)
 $644万
 $21,056/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -84486,7 +84486,7 @@
           <t>H | 306呎 (1房)
 $647万
 $21,137/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -84494,7 +84494,7 @@
           <t>J | 308呎 (1房)
 $651万
 $21,136/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr">
@@ -84502,7 +84502,7 @@
           <t>K | 426呎 (2房)
 $891万
 $20,906/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
@@ -84510,7 +84510,7 @@
           <t>L | 305呎 (1房)
 $666万
 $21,830/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -84518,7 +84518,7 @@
           <t>M | 429呎 (2房)
 $951万
 $22,159/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
@@ -84526,7 +84526,7 @@
           <t>N | 278呎 (1房)
 $638万
 $22,964/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -84581,7 +84581,7 @@
           <t>F | 307呎 (1房)
 $638万
 $20,782/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -84589,7 +84589,7 @@
           <t>G | 306呎 (1房)
 $638万
 $20,850/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -84597,7 +84597,7 @@
           <t>H | 306呎 (1房)
 $641万
 $20,935/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -84605,7 +84605,7 @@
           <t>J | 308呎 (1房)
 $645万
 $20,929/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -84613,7 +84613,7 @@
           <t>K | 426呎 (2房)
 $882万
 $20,692/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
@@ -84621,7 +84621,7 @@
           <t>L | 305呎 (1房)
 $659万
 $21,613/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="M11" s="23" t="inlineStr">
@@ -84629,7 +84629,7 @@
           <t>M | 429呎 (2房)
 $941万
 $21,939/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
@@ -84637,7 +84637,7 @@
           <t>N | 278呎 (1房)
 $632万
 $22,737/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -84652,7 +84652,7 @@
           <t>A | 613呎 (2房)
 $1566万
 $25,540/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -84660,7 +84660,7 @@
           <t>B | 486呎 (2房)
 $1217万
 $25,035/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -84668,7 +84668,7 @@
           <t>C | 548呎 (2房)
 $1330万
 $24,279/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -84676,7 +84676,7 @@
           <t>D | 432呎 (2房)
 $1063万
 $24,597/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -84684,7 +84684,7 @@
           <t>E | 499呎 (2房)
 $1213万
 $24,305/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -84692,7 +84692,7 @@
           <t>F | 307呎 (1房)
 $620万
 $20,189/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -84700,7 +84700,7 @@
           <t>G | 306呎 (1房)
 $620万
 $20,255/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -84708,7 +84708,7 @@
           <t>H | 306呎 (1房)
 $622万
 $20,310/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -84716,7 +84716,7 @@
           <t>J | 308呎 (1房)
 $626万
 $20,308/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -84724,7 +84724,7 @@
           <t>K | 426呎 (2房)
 $856万
 $20,099/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L12" s="23" t="inlineStr">
@@ -84732,7 +84732,7 @@
           <t>L | 305呎 (1房)
 $665万
 $21,816/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -84740,7 +84740,7 @@
           <t>M | 429呎 (2房)
 $913万
 $21,287/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -84748,7 +84748,7 @@
           <t>N | 278呎 (1房)
 $614万
 $22,068/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -84763,7 +84763,7 @@
           <t>A | 613呎 (2房)
 $1476万
 $24,078/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -84771,7 +84771,7 @@
           <t>B | 486呎 (2房)
 $1158万
 $23,831/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -84779,7 +84779,7 @@
           <t>C | 548呎 (2房)
 $1317万
 $24,038/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -84795,7 +84795,7 @@
           <t>E | 499呎 (2房)
 $1172万
 $23,477/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -84803,7 +84803,7 @@
           <t>F | 307呎 (1房)
 $613万
 $19,977/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -84811,7 +84811,7 @@
           <t>G | 306呎 (1房)
 $613万
 $20,042/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -84819,7 +84819,7 @@
           <t>H | 306呎 (1房)
 $615万
 $20,108/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -84827,7 +84827,7 @@
           <t>J | 308呎 (1房)
 $620万
 $20,117/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
@@ -84835,7 +84835,7 @@
           <t>K | 426呎 (2房)
 $847万
 $19,887/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -84843,7 +84843,7 @@
           <t>L | 305呎 (1房)
 $634万
 $20,770/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -84851,7 +84851,7 @@
           <t>M | 429呎 (2房)
 $941万
 $21,928/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
@@ -84859,7 +84859,7 @@
           <t>N | 278呎 (1房)
 $608万
 $21,863/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -84890,7 +84890,7 @@
           <t>C | 548呎 (2房)
 $1399万
 $25,526/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -84914,7 +84914,7 @@
           <t>F | 307呎 (1房)
 $607万
 $19,772/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -84922,7 +84922,7 @@
           <t>G | 306呎 (1房)
 $607万
 $19,837/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -84930,7 +84930,7 @@
           <t>H | 306呎 (1房)
 $609万
 $19,908/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -84938,7 +84938,7 @@
           <t>J | 308呎 (1房)
 $638万
 $20,708/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr">
@@ -84946,7 +84946,7 @@
           <t>K | 426呎 (2房)
 $839万
 $19,690/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L14" s="23" t="inlineStr">
@@ -84954,7 +84954,7 @@
           <t>L | 305呎 (1房)
 $628万
 $20,577/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -84962,7 +84962,7 @@
           <t>M | 429呎 (2房)
 $896万
 $20,876/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="N14" s="23" t="inlineStr">
@@ -84970,7 +84970,7 @@
           <t>N | 278呎 (1房)
 $614万
 $22,068/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -84985,7 +84985,7 @@
           <t>A | 613呎 (2房)
 $1534万
 $25,021/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -85001,7 +85001,7 @@
           <t>C | 548呎 (2房)
 $1369万
 $24,978/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -85025,7 +85025,7 @@
           <t>F | 307呎 (1房)
 $601万
 $19,577/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -85033,7 +85033,7 @@
           <t>G | 306呎 (1房)
 $601万
 $19,641/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -85041,7 +85041,7 @@
           <t>H | 306呎 (1房)
 $603万
 $19,712/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -85049,7 +85049,7 @@
           <t>J | 308呎 (1房)
 $608万
 $19,727/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr">
@@ -85057,7 +85057,7 @@
           <t>K | 426呎 (2房)
 $830万
 $19,495/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
@@ -85065,7 +85065,7 @@
           <t>L | 305呎 (1房)
 $621万
 $20,367/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -85073,7 +85073,7 @@
           <t>M | 429呎 (2房)
 $887万
 $20,667/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
@@ -85081,7 +85081,7 @@
           <t>N | 278呎 (1房)
 $596万
 $21,421/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -85096,7 +85096,7 @@
           <t>A | 613呎 (2房)
 $1433万
 $23,370/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -85104,7 +85104,7 @@
           <t>B | 486呎 (2房)
 $1124万
 $23,132/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -85112,7 +85112,7 @@
           <t>C | 548呎 (2房)
 $1278万
 $23,330/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -85120,7 +85120,7 @@
           <t>D | 432呎 (2房)
 $1001万
 $23,167/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -85128,7 +85128,7 @@
           <t>E | 499呎 (2房)
 $1137万
 $22,786/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -85136,7 +85136,7 @@
           <t>F | 307呎 (1房)
 $595万
 $19,388/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -85144,7 +85144,7 @@
           <t>G | 306呎 (1房)
 $595万
 $19,451/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -85152,7 +85152,7 @@
           <t>H | 306呎 (1房)
 $597万
 $19,516/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -85160,7 +85160,7 @@
           <t>J | 308呎 (1房)
 $601万
 $19,506/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -85168,7 +85168,7 @@
           <t>K | 426呎 (2房)
 $822万
 $19,308/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -85176,7 +85176,7 @@
           <t>L | 305呎 (1房)
 $615万
 $20,170/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -85184,7 +85184,7 @@
           <t>M | 429呎 (2房)
 $878万
 $20,462/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N16" s="23" t="inlineStr">
@@ -85192,7 +85192,7 @@
           <t>N | 278呎 (1房)
 $590万
 $21,216/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -85207,7 +85207,7 @@
           <t>A | 613呎 (2房)
 $1426万
 $23,263/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -85215,7 +85215,7 @@
           <t>B | 486呎 (2房)
 $1119万
 $23,016/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -85223,7 +85223,7 @@
           <t>C | 548呎 (2房)
 $1272万
 $23,215/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -85231,7 +85231,7 @@
           <t>D | 432呎 (2房)
 $996万
 $23,056/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -85239,7 +85239,7 @@
           <t>E | 499呎 (2房)
 $1177万
 $23,583/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -85247,7 +85247,7 @@
           <t>F | 307呎 (1房)
 $593万
 $19,326/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -85255,7 +85255,7 @@
           <t>G | 306呎 (1房)
 $593万
 $19,389/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -85263,7 +85263,7 @@
           <t>H | 306呎 (1房)
 $596万
 $19,461/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -85271,7 +85271,7 @@
           <t>J | 308呎 (1房)
 $600万
 $19,464/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -85279,7 +85279,7 @@
           <t>K | 426呎 (2房)
 $820万
 $19,249/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -85287,7 +85287,7 @@
           <t>L | 305呎 (1房)
 $613万
 $20,105/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -85295,7 +85295,7 @@
           <t>M | 429呎 (2房)
 $875万
 $20,401/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
@@ -85303,7 +85303,7 @@
           <t>N | 278呎 (1房)
 $587万
 $21,101/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -85318,7 +85318,7 @@
           <t>A | 613呎 (2房)
 $1418万
 $23,132/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -85326,7 +85326,7 @@
           <t>B | 486呎 (2房)
 $1113万
 $22,901/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -85334,7 +85334,7 @@
           <t>C | 548呎 (2房)
 $1266万
 $23,099/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -85342,7 +85342,7 @@
           <t>D | 432呎 (2房)
 $991万
 $22,940/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -85350,7 +85350,7 @@
           <t>E | 499呎 (2房)
 $1126万
 $22,557/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -85358,7 +85358,7 @@
           <t>F | 307呎 (1房)
 $592万
 $19,267/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -85366,7 +85366,7 @@
           <t>G | 306呎 (1房)
 $592万
 $19,330/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -85374,7 +85374,7 @@
           <t>H | 306呎 (1房)
 $594万
 $19,405/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -85382,7 +85382,7 @@
           <t>J | 308呎 (1房)
 $598万
 $19,399/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -85390,7 +85390,7 @@
           <t>K | 426呎 (2房)
 $818万
 $19,190/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -85398,7 +85398,7 @@
           <t>L | 305呎 (1房)
 $611万
 $20,039/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -85406,7 +85406,7 @@
           <t>M | 429呎 (2房)
 $873万
 $20,340/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -85414,7 +85414,7 @@
           <t>N | 278呎 (1房)
 $584万
 $21,000/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -85429,7 +85429,7 @@
           <t>A | 613呎 (2房)
 $1440万
 $23,488/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -85437,7 +85437,7 @@
           <t>B | 486呎 (2房)
 $1143万
 $23,514/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -85445,7 +85445,7 @@
           <t>C | 548呎 (2房)
 $1285万
 $23,445/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -85453,7 +85453,7 @@
           <t>D | 432呎 (2房)
 $1016万
 $23,523/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -85461,7 +85461,7 @@
           <t>E | 499呎 (2房)
 $1149万
 $23,022/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -85469,7 +85469,7 @@
           <t>F | 307呎 (1房)
 $608万
 $19,792/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -85477,7 +85477,7 @@
           <t>G | 306呎 (1房)
 $608万
 $19,856/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -85485,7 +85485,7 @@
           <t>H | 306呎 (1房)
 $610万
 $19,928/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -85493,7 +85493,7 @@
           <t>J | 308呎 (1房)
 $614万
 $19,929/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -85501,7 +85501,7 @@
           <t>K | 426呎 (2房)
 $844万
 $19,808/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
@@ -85509,7 +85509,7 @@
           <t>L | 305呎 (1房)
 $628万
 $20,584/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M19" s="23" t="inlineStr">
@@ -85517,7 +85517,7 @@
           <t>M | 429呎 (2房)
 $901万
 $20,998/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
@@ -85525,7 +85525,7 @@
           <t>N | 278呎 (1房)
 $599万
 $21,540/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -85580,7 +85580,7 @@
           <t>F | 307呎 (1房)
 $606万
 $19,739/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -85588,7 +85588,7 @@
           <t>G | 306呎 (1房)
 $606万
 $19,791/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -85596,7 +85596,7 @@
           <t>H | 306呎 (1房)
 $608万
 $19,863/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -85604,7 +85604,7 @@
           <t>J | 308呎 (1房)
 $612万
 $19,864/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
@@ -85612,7 +85612,7 @@
           <t>K | 426呎 (2房)
 $842万
 $19,761/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -85620,7 +85620,7 @@
           <t>L | 305呎 (1房)
 $626万
 $20,525/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
@@ -85628,7 +85628,7 @@
           <t>M | 429呎 (2房)
 $899万
 $20,951/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
@@ -85636,7 +85636,7 @@
           <t>N | 278呎 (1房)
 $595万
 $21,410/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -85651,7 +85651,7 @@
           <t>A | 613呎 (2房)
 $1445万
 $23,579/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -85659,7 +85659,7 @@
           <t>B | 486呎 (2房)
 $1091万
 $22,449/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -85667,7 +85667,7 @@
           <t>C | 548呎 (2房)
 $1240万
 $22,620/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -85675,7 +85675,7 @@
           <t>D | 432呎 (2房)
 $972万
 $22,491/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -85683,7 +85683,7 @@
           <t>E | 499呎 (2房)
 $1149万
 $23,022/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -85691,7 +85691,7 @@
           <t>F | 307呎 (1房)
 $582万
 $18,967/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -85699,7 +85699,7 @@
           <t>G | 306呎 (1房)
 $606万
 $19,791/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -85707,7 +85707,7 @@
           <t>H | 306呎 (1房)
 $584万
 $19,101/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -85715,7 +85715,7 @@
           <t>J | 308呎 (1房)
 $588万
 $19,097/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
@@ -85723,7 +85723,7 @@
           <t>K | 426呎 (2房)
 $804万
 $18,885/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -85731,7 +85731,7 @@
           <t>L | 305呎 (1房)
 $602万
 $19,725/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="M21" s="23" t="inlineStr">
@@ -85739,7 +85739,7 @@
           <t>M | 429呎 (2房)
 $893万
 $20,818/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
@@ -85747,7 +85747,7 @@
           <t>N | 278呎 (1房)
 $590万
 $21,205/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -85762,7 +85762,7 @@
           <t>A | 613呎 (2房)
 $1438万
 $23,460/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -85770,7 +85770,7 @@
           <t>B | 486呎 (2房)
 $1087万
 $22,358/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -85778,7 +85778,7 @@
           <t>C | 548呎 (2房)
 $1235万
 $22,536/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -85786,7 +85786,7 @@
           <t>D | 432呎 (2房)
 $967万
 $22,380/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -85794,7 +85794,7 @@
           <t>E | 499呎 (2房)
 $1098万
 $22,000/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -85802,7 +85802,7 @@
           <t>F | 307呎 (1房)
 $580万
 $18,909/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -85810,7 +85810,7 @@
           <t>G | 306呎 (1房)
 $580万
 $18,971/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -85818,7 +85818,7 @@
           <t>H | 306呎 (1房)
 $582万
 $19,036/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -85826,7 +85826,7 @@
           <t>J | 308呎 (1房)
 $587万
 $19,052/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -85834,7 +85834,7 @@
           <t>K | 426呎 (2房)
 $802万
 $18,826/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -85842,7 +85842,7 @@
           <t>L | 305呎 (1房)
 $600万
 $19,666/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -85850,7 +85850,7 @@
           <t>M | 429呎 (2房)
 $856万
 $19,958/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -85858,7 +85858,7 @@
           <t>N | 278呎 (1房)
 $570万
 $20,486/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -85873,7 +85873,7 @@
           <t>A | 613呎 (2房)
 $1376万
 $22,447/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -85881,7 +85881,7 @@
           <t>B | 486呎 (2房)
 $1080万
 $22,222/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -85889,7 +85889,7 @@
           <t>C | 548呎 (2房)
 $1228万
 $22,412/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -85897,7 +85897,7 @@
           <t>D | 432呎 (2房)
 $962万
 $22,264/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -85913,7 +85913,7 @@
           <t>F | 307呎 (1房)
 $579万
 $18,853/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -85921,7 +85921,7 @@
           <t>G | 306呎 (1房)
 $579万
 $18,915/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -85929,7 +85929,7 @@
           <t>H | 306呎 (1房)
 $581万
 $18,980/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -85937,7 +85937,7 @@
           <t>J | 308呎 (1房)
 $585万
 $18,981/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr">
@@ -85945,7 +85945,7 @@
           <t>K | 426呎 (2房)
 $800万
 $18,775/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
@@ -85953,7 +85953,7 @@
           <t>L | 305呎 (1房)
 $598万
 $19,607/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="M23" s="23" t="inlineStr">
@@ -85961,7 +85961,7 @@
           <t>M | 429呎 (2房)
 $854万
 $19,900/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -85969,7 +85969,7 @@
           <t>N | 278呎 (1房)
 $584万
 $20,989/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -85984,7 +85984,7 @@
           <t>A | 613呎 (2房)
 $1369万
 $22,336/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -85992,7 +85992,7 @@
           <t>B | 486呎 (2房)
 $1075万
 $22,111/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -86000,7 +86000,7 @@
           <t>C | 548呎 (2房)
 $1222万
 $22,301/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -86008,7 +86008,7 @@
           <t>D | 432呎 (2房)
 $957万
 $22,148/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -86016,7 +86016,7 @@
           <t>E | 499呎 (2房)
 $1087万
 $21,780/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -86024,7 +86024,7 @@
           <t>F | 307呎 (1房)
 $577万
 $18,795/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -86032,7 +86032,7 @@
           <t>G | 306呎 (1房)
 $577万
 $18,856/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -86040,7 +86040,7 @@
           <t>H | 306呎 (1房)
 $579万
 $18,928/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -86048,7 +86048,7 @@
           <t>J | 308呎 (1房)
 $583万
 $18,922/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -86056,7 +86056,7 @@
           <t>K | 426呎 (2房)
 $798万
 $18,721/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -86064,7 +86064,7 @@
           <t>L | 305呎 (1房)
 $596万
 $19,548/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
@@ -86072,7 +86072,7 @@
           <t>M | 429呎 (2房)
 $851万
 $19,837/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
@@ -86080,7 +86080,7 @@
           <t>N | 278呎 (1房)
 $564万
 $20,273/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -86095,7 +86095,7 @@
           <t>A | 613呎 (2房)
 $1390万
 $22,672/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -86103,7 +86103,7 @@
           <t>B | 486呎 (2房)
 $1108万
 $22,798/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -86111,7 +86111,7 @@
           <t>C | 548呎 (2房)
 $1241万
 $22,642/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -86119,7 +86119,7 @@
           <t>D | 432呎 (2房)
 $971万
 $22,481/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -86127,7 +86127,7 @@
           <t>E | 499呎 (2房)
 $1131万
 $22,665/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -86135,7 +86135,7 @@
           <t>F | 307呎 (1房)
 $593万
 $19,309/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -86143,7 +86143,7 @@
           <t>G | 306呎 (1房)
 $593万
 $19,373/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -86151,7 +86151,7 @@
           <t>H | 306呎 (1房)
 $595万
 $19,431/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -86159,7 +86159,7 @@
           <t>J | 308呎 (1房)
 $599万
 $19,435/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -86167,7 +86167,7 @@
           <t>K | 426呎 (2房)
 $824万
 $19,338/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -86175,7 +86175,7 @@
           <t>L | 305呎 (1房)
 $612万
 $20,072/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M25" s="23" t="inlineStr">
@@ -86183,7 +86183,7 @@
           <t>M | 429呎 (2房)
 $879万
 $20,485/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
@@ -86191,7 +86191,7 @@
           <t>N | 278呎 (1房)
 $581万
 $20,892/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -86206,7 +86206,7 @@
           <t>A | 613呎 (2房)
 $1430万
 $23,328/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -86214,7 +86214,7 @@
           <t>B | 486呎 (2房)
 $1123万
 $23,103/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -86222,7 +86222,7 @@
           <t>C | 548呎 (2房)
 $1269万
 $23,153/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -86246,7 +86246,7 @@
           <t>F | 307呎 (1房)
 $591万
 $19,251/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -86254,7 +86254,7 @@
           <t>G | 306呎 (1房)
 $591万
 $19,307/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -86262,7 +86262,7 @@
           <t>H | 306呎 (1房)
 $593万
 $19,379/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -86270,7 +86270,7 @@
           <t>J | 308呎 (1房)
 $597万
 $19,377/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -86278,7 +86278,7 @@
           <t>K | 426呎 (2房)
 $821万
 $19,268/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -86286,7 +86286,7 @@
           <t>L | 305呎 (1房)
 $611万
 $20,020/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -86294,7 +86294,7 @@
           <t>M | 429呎 (2房)
 $877万
 $20,438/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
@@ -86302,7 +86302,7 @@
           <t>N | 278呎 (1房)
 $578万
 $20,773/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -86317,7 +86317,7 @@
           <t>A | 613呎 (2房)
 $1336万
 $21,786/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -86325,7 +86325,7 @@
           <t>B | 486呎 (2房)
 $1048万
 $21,570/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -86333,7 +86333,7 @@
           <t>C | 548呎 (2房)
 $1174万
 $21,432/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -86341,7 +86341,7 @@
           <t>D | 432呎 (2房)
 $920万
 $21,292/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -86349,7 +86349,7 @@
           <t>E | 499呎 (2房)
 $1081万
 $21,659/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -86357,7 +86357,7 @@
           <t>F | 307呎 (1房)
 $572万
 $18,625/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -86365,7 +86365,7 @@
           <t>G | 306呎 (1房)
 $572万
 $18,686/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -86373,7 +86373,7 @@
           <t>H | 306呎 (1房)
 $574万
 $18,752/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -86381,7 +86381,7 @@
           <t>J | 308呎 (1房)
 $578万
 $18,753/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -86389,7 +86389,7 @@
           <t>K | 426呎 (2房)
 $790万
 $18,549/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -86397,7 +86397,7 @@
           <t>L | 305呎 (1房)
 $591万
 $19,370/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="M27" s="23" t="inlineStr">
@@ -86405,7 +86405,7 @@
           <t>M | 429呎 (2房)
 $844万
 $19,662/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
@@ -86413,7 +86413,7 @@
           <t>N | 278呎 (1房)
 $574万
 $20,640/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -86428,7 +86428,7 @@
           <t>A | 613呎 (2房)
 $1349万
 $22,003/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -86436,7 +86436,7 @@
           <t>B | 486呎 (2房)
 $1068万
 $21,975/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -86444,7 +86444,7 @@
           <t>C | 548呎 (2房)
 $1180万
 $21,533/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -86452,7 +86452,7 @@
           <t>D | 432呎 (2房)
 $906万
 $20,972/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -86460,343 +86460,10 @@
           <t>E | 499呎 (2房)
 $1047万
 $20,978/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$569万
-$18,541/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$569万
-$18,601/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$571万
-$18,660/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$575万
-$18,662/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>K | 426呎 (2房)
-$786万
-$18,455/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="L28" s="23" t="inlineStr">
-        <is>
-          <t>L | 305呎 (1房)
-$588万
-$19,272/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="M28" s="23" t="inlineStr">
-        <is>
-          <t>M | 429呎 (2房)
-$839万
-$19,562/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="N28" s="23" t="inlineStr">
-        <is>
-          <t>N | 278呎 (1房)
-$570万
-$20,486/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 613呎 (2房)
-$1377万
-$22,460/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>B | 486呎 (2房)
-$1081万
-$22,239/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>C | 548呎 (2房)
-$1207万
-$22,022/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$888万
-$20,562/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$564万
-$18,355/呎
-(26年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$564万
-$18,415/呎
-(26年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="I29" s="23" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$566万
-$18,480/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$569万
-$18,481/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>K | 426呎 (2房)
-$779万
-$18,282/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="L29" s="23" t="inlineStr">
-        <is>
-          <t>L | 305呎 (1房)
-$582万
-$19,089/呎
-(26年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="M29" s="23" t="inlineStr">
-        <is>
-          <t>M | 429呎 (2房)
-$831万
-$19,375/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="N29" s="23" t="inlineStr">
-        <is>
-          <t>N | 278呎 (1房)
-$565万
-$20,317/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>A | 613呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 486呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>C | 548呎 (2房)
-$1209万
-$22,058/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$843万
-$19,505/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>E | 443呎 (2房)
-$807万
-$18,212/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>F | 307呎 (1房)
-$583万
-$18,990/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>G | 306呎 (1房)
-$560万
-$18,301/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>H | 306呎 (1房)
-$563万
-$18,386/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>J | 308呎 (1房)
-$566万
-$18,383/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>K | 426呎 (2房)
-$775万
-$18,192/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>L | 305呎 (1房)
-$579万
-$18,990/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>M | 429呎 (2房)
-$823万
-$19,179/呎
-(26年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="N30" s="23" t="inlineStr">
-        <is>
-          <t>N | 278呎 (1房)
-$563万
-$20,245/呎
-(26年-05月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>A | 613呎 (2房)
-$1326万
-$21,631/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>B | 486呎 (2房)
-$1041万
-$21,416/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>C | 548呎 (2房)
-$1159万
-$21,146/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$821万
-$19,000/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>E | 443呎 (2房)
-$799万
-$18,032/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $569万
@@ -86804,7 +86471,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $569万
@@ -86812,44 +86479,377 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="I31" s="23" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $571万
 $18,660/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $575万
 $18,662/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
 $786万
 $18,455/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="L31" s="23" t="inlineStr">
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>L | 305呎 (1房)
 $588万
 $19,272/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="M31" s="23" t="inlineStr">
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="M28" s="23" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $839万
 $19,562/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>N | 278呎 (1房)
+$570万
+$20,486/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 613呎 (2房)
+$1377万
+$22,460/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 486呎 (2房)
+$1081万
+$22,239/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 548呎 (2房)
+$1207万
+$22,022/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$888万
+$20,562/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$564万
+$18,355/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$564万
+$18,415/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$566万
+$18,480/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$569万
+$18,481/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>K | 426呎 (2房)
+$779万
+$18,282/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>L | 305呎 (1房)
+$582万
+$19,089/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr">
+        <is>
+          <t>M | 429呎 (2房)
+$831万
+$19,375/呎
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t>N | 278呎 (1房)
+$565万
+$20,317/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 613呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 486呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 548呎 (2房)
+$1209万
+$22,058/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$843万
+$19,505/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 443呎 (2房)
+$807万
+$18,212/呎
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$583万
+$18,990/呎
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$560万
+$18,301/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$563万
+$18,386/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$566万
+$18,383/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>K | 426呎 (2房)
+$775万
+$18,192/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>L | 305呎 (1房)
+$579万
+$18,990/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="M30" s="23" t="inlineStr">
+        <is>
+          <t>M | 429呎 (2房)
+$823万
+$19,179/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>N | 278呎 (1房)
+$563万
+$20,245/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 613呎 (2房)
+$1326万
+$21,631/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 486呎 (2房)
+$1041万
+$21,416/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 548呎 (2房)
+$1159万
+$21,146/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$821万
+$19,000/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 443呎 (2房)
+$799万
+$18,032/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 307呎 (1房)
+$569万
+$18,541/呎
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 306呎 (1房)
+$569万
+$18,601/呎
+(26年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 306呎 (1房)
+$571万
+$18,660/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 308呎 (1房)
+$575万
+$18,662/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>K | 426呎 (2房)
+$786万
+$18,455/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>L | 305呎 (1房)
+$588万
+$19,272/呎
 (26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr">
+        <is>
+          <t>M | 429呎 (2房)
+$839万
+$19,562/呎
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -86857,7 +86857,7 @@
           <t>N | 278呎 (1房)
 $561万
 $20,173/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -86880,7 +86880,7 @@
           <t>B | 486呎 (2房)
 $1050万
 $21,601/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -86888,7 +86888,7 @@
           <t>C | 550呎 (2房)
 $1178万
 $21,418/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr"/>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -55790,7 +55790,7 @@
       </c>
       <c r="G791" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H791" s="5" t="n">
@@ -56507,23 +56507,23 @@
       </c>
       <c r="F802" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G802" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H802" s="5" t="n">
-        <v>8944000</v>
+        <v>6708000</v>
       </c>
       <c r="I802" s="5" t="n">
-        <v>32173</v>
+        <v>24129</v>
       </c>
       <c r="J802" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K802" s="5" t="n">
@@ -56534,7 +56534,7 @@
       </c>
       <c r="M802" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N802" s="3" t="inlineStr">
@@ -63039,38 +63039,30 @@
       </c>
       <c r="F904" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G904" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H904" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I904" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H904" s="5" t="n">
+        <v>12038000</v>
+      </c>
+      <c r="I904" s="5" t="n">
+        <v>24770</v>
       </c>
       <c r="J904" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K904" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L904" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K904" s="5" t="n">
+        <v>12038000</v>
+      </c>
+      <c r="L904" s="5" t="n">
+        <v>24770</v>
       </c>
       <c r="M904" s="3" t="inlineStr">
         <is>
@@ -63079,7 +63071,7 @@
       </c>
       <c r="N904" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -74470,7 +74462,7 @@
       </c>
       <c r="G1087" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H1087" s="5" t="n">
@@ -75209,38 +75201,30 @@
       </c>
       <c r="F1099" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1099" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1099" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1099" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H1099" s="5" t="n">
+        <v>10808000</v>
+      </c>
+      <c r="I1099" s="5" t="n">
+        <v>22239</v>
       </c>
       <c r="J1099" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1099" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1099" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1099" s="5" t="n">
+        <v>10808000</v>
+      </c>
+      <c r="L1099" s="5" t="n">
+        <v>22239</v>
       </c>
       <c r="M1099" s="3" t="inlineStr">
         <is>
@@ -75249,7 +75233,7 @@
       </c>
       <c r="N1099" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -76098,7 +76082,7 @@
       </c>
       <c r="G1113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H1113" s="5" t="n">
@@ -83768,7 +83752,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -83778,7 +83762,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84177,7 +84161,7 @@
           <t>L | 305呎 (1房)
 $732万
 $24,000/呎
-(26年-07月-08日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -84299,12 +84283,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
-$894万
-$32,173/呎
-(在售)</t>
+$671万
+$24,129/呎
+(26年-08月-09日)</t>
         </is>
       </c>
     </row>
@@ -84988,12 +84972,12 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
-招标单位
--
-(在售)</t>
+$1204万
+$24,770/呎
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -86539,7 +86523,7 @@
           <t>A | 613呎 (2房)
 $1377万
 $22,460/呎
-(26年-07月-08日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -86653,12 +86637,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
-招标单位
--
-(在售)</t>
+$1081万
+$22,239/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -86761,7 +86745,7 @@
           <t>A | 613呎 (2房)
 $1326万
 $21,631/呎
-(26年-07月-16日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -62271,38 +62271,30 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G892" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H892" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I892" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H892" s="5" t="n">
+        <v>15818000</v>
+      </c>
+      <c r="I892" s="5" t="n">
+        <v>25804</v>
       </c>
       <c r="J892" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K892" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L892" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K892" s="5" t="n">
+        <v>15818000</v>
+      </c>
+      <c r="L892" s="5" t="n">
+        <v>25804</v>
       </c>
       <c r="M892" s="3" t="inlineStr">
         <is>
@@ -62311,7 +62303,7 @@
       </c>
       <c r="N892" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -76634,7 +76626,7 @@
       </c>
       <c r="G1121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H1121" s="5" t="n">
@@ -76696,7 +76688,7 @@
       </c>
       <c r="G1122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H1122" s="5" t="n">
@@ -83752,7 +83744,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -83762,7 +83754,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -84853,12 +84845,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 613呎 (2房)
-招标单位
--
-(在售)</t>
+$1582万
+$25,804/呎
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -86864,7 +86856,7 @@
           <t>B | 486呎 (2房)
 $1050万
 $21,601/呎
-(26年-07月-20日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -86872,7 +86864,7 @@
           <t>C | 550呎 (2房)
 $1178万
 $21,418/呎
-(26年-07月-20日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr"/>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -70958,7 +70958,7 @@
       </c>
       <c r="G1031" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H1031" s="5" t="n">
@@ -86103,7 +86103,7 @@
           <t>E | 499呎 (2房)
 $1131万
 $22,665/呎
-(26年-07月-14日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -61999,38 +61999,30 @@
       </c>
       <c r="F888" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G888" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H888" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I888" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H888" s="5" t="n">
+        <v>12376000</v>
+      </c>
+      <c r="I888" s="5" t="n">
+        <v>24802</v>
       </c>
       <c r="J888" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K888" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L888" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K888" s="5" t="n">
+        <v>12376000</v>
+      </c>
+      <c r="L888" s="5" t="n">
+        <v>24802</v>
       </c>
       <c r="M888" s="3" t="inlineStr">
         <is>
@@ -62039,7 +62031,7 @@
       </c>
       <c r="N888" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -66875,7 +66867,7 @@
       </c>
       <c r="F966" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G966" s="3" t="inlineStr">
@@ -66885,12 +66877,12 @@
       </c>
       <c r="H966" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I966" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J966" s="3" t="inlineStr">
@@ -66900,12 +66892,12 @@
       </c>
       <c r="K966" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L966" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M966" s="3" t="inlineStr">
@@ -66915,7 +66907,7 @@
       </c>
       <c r="N966" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -67015,38 +67007,30 @@
       </c>
       <c r="F968" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G968" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H968" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I968" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H968" s="5" t="n">
+        <v>12988000</v>
+      </c>
+      <c r="I968" s="5" t="n">
+        <v>23701</v>
       </c>
       <c r="J968" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K968" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L968" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K968" s="5" t="n">
+        <v>12988000</v>
+      </c>
+      <c r="L968" s="5" t="n">
+        <v>23701</v>
       </c>
       <c r="M968" s="3" t="inlineStr">
         <is>
@@ -67055,7 +67039,7 @@
       </c>
       <c r="N968" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -71759,7 +71743,7 @@
       </c>
       <c r="F1044" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1044" s="3" t="inlineStr">
@@ -71769,12 +71753,12 @@
       </c>
       <c r="H1044" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1044" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1044" s="3" t="inlineStr">
@@ -71784,12 +71768,12 @@
       </c>
       <c r="K1044" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1044" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1044" s="3" t="inlineStr">
@@ -71799,7 +71783,7 @@
       </c>
       <c r="N1044" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -75255,7 +75239,7 @@
       </c>
       <c r="F1100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1100" s="3" t="inlineStr">
@@ -75265,12 +75249,12 @@
       </c>
       <c r="H1100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1100" s="3" t="inlineStr">
@@ -75280,12 +75264,12 @@
       </c>
       <c r="K1100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1100" s="3" t="inlineStr">
@@ -75295,7 +75279,7 @@
       </c>
       <c r="N1100" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -76131,38 +76115,30 @@
       </c>
       <c r="F1114" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1114" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1114" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1114" s="5" t="n">
+        <v>17720000</v>
+      </c>
+      <c r="I1114" s="5" t="n">
+        <v>26527</v>
       </c>
       <c r="J1114" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1114" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1114" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1114" s="5" t="n">
+        <v>17720000</v>
+      </c>
+      <c r="L1114" s="5" t="n">
+        <v>26527</v>
       </c>
       <c r="M1114" s="3" t="inlineStr">
         <is>
@@ -76171,7 +76147,7 @@
       </c>
       <c r="N1114" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -76271,38 +76247,30 @@
       </c>
       <c r="F1116" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I1116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1116" s="5" t="n">
+        <v>8308000</v>
+      </c>
+      <c r="I1116" s="5" t="n">
+        <v>19502</v>
       </c>
       <c r="J1116" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L1116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K1116" s="5" t="n">
+        <v>8308000</v>
+      </c>
+      <c r="L1116" s="5" t="n">
+        <v>19502</v>
       </c>
       <c r="M1116" s="3" t="inlineStr">
         <is>
@@ -76745,7 +76713,7 @@
       </c>
       <c r="F1123" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1123" s="3" t="inlineStr">
@@ -76755,12 +76723,12 @@
       </c>
       <c r="H1123" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I1123" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1123" s="3" t="inlineStr">
@@ -76770,12 +76738,12 @@
       </c>
       <c r="K1123" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L1123" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1123" s="3" t="inlineStr">
@@ -76785,7 +76753,7 @@
       </c>
       <c r="N1123" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -83744,7 +83712,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -83754,7 +83722,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83764,7 +83732,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -84877,12 +84845,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-招标单位
--
-(在售)</t>
+$1238万
+$24,802/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -85527,12 +85495,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1299万
+$23,701/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -85543,12 +85511,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -86209,12 +86177,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -86621,12 +86589,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 613呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -86843,12 +86811,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -86901,28 +86869,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
+$831万
+$19,502/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 307呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>L | 307呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="M32" s="20" t="inlineStr">
+      <c r="M32" s="23" t="inlineStr">
         <is>
           <t>M | 668呎 (3房)
-招标单位
--
-(在售)</t>
+$1772万
+$26,527/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr"/>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -288,10 +288,10 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="N143" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M154" s="3" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -11140,12 +11140,12 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M156" s="3" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -11280,12 +11280,12 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr">
@@ -11295,12 +11295,12 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="N157" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15450,31 +15450,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" s="5" t="n">
-        <v>13317000</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>30474</v>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>9987750</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>22855</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15512,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15512,31 +15520,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" s="5" t="n">
-        <v>16496000</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>30891</v>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K220" s="5" t="n">
-        <v>12372000</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>23169</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15582,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15574,31 +15590,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>14437000</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>28990</v>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>10827750</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>21742</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15652,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15636,31 +15660,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" s="5" t="n">
-        <v>16762000</v>
-      </c>
-      <c r="I222" s="5" t="n">
-        <v>31272</v>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>12571500</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>23454</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15722,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -16256,7 +16288,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -16264,31 +16296,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H232" s="5" t="n">
-        <v>13237000</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>30291</v>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K232" s="5" t="n">
-        <v>9927750</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>22718</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16358,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16326,31 +16366,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="5" t="n">
-        <v>16394000</v>
-      </c>
-      <c r="I233" s="5" t="n">
-        <v>30700</v>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K233" s="5" t="n">
-        <v>12295500</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>23025</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16428,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16388,31 +16436,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H234" s="5" t="n">
-        <v>14357000</v>
-      </c>
-      <c r="I234" s="5" t="n">
-        <v>28829</v>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>10767750</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>21622</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16442,7 +16498,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16450,31 +16506,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H235" s="5" t="n">
-        <v>16661000</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>31084</v>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K235" s="5" t="n">
-        <v>12495750</v>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v>23313</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16568,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -17350,7 +17414,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -19736,7 +19800,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19744,31 +19808,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H284" s="5" t="n">
-        <v>12917000</v>
-      </c>
-      <c r="I284" s="5" t="n">
-        <v>29558</v>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K284" s="5" t="n">
-        <v>9687750</v>
-      </c>
-      <c r="L284" s="5" t="n">
-        <v>22169</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19798,7 +19870,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -19806,31 +19878,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H285" s="5" t="n">
-        <v>16010000</v>
-      </c>
-      <c r="I285" s="5" t="n">
-        <v>29981</v>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K285" s="5" t="n">
-        <v>12007500</v>
-      </c>
-      <c r="L285" s="5" t="n">
-        <v>22486</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19860,7 +19940,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -19868,31 +19948,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H286" s="5" t="n">
-        <v>14010000</v>
-      </c>
-      <c r="I286" s="5" t="n">
-        <v>28133</v>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K286" s="5" t="n">
-        <v>10507500</v>
-      </c>
-      <c r="L286" s="5" t="n">
-        <v>21099</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20080,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -20558,7 +20646,7 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -20566,31 +20654,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H297" s="5" t="n">
-        <v>12850000</v>
-      </c>
-      <c r="I297" s="5" t="n">
-        <v>29405</v>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K297" s="5" t="n">
-        <v>9637500</v>
-      </c>
-      <c r="L297" s="5" t="n">
-        <v>22054</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N297" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20620,7 +20716,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -20628,31 +20724,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H298" s="5" t="n">
-        <v>15917000</v>
-      </c>
-      <c r="I298" s="5" t="n">
-        <v>29807</v>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K298" s="5" t="n">
-        <v>11937750</v>
-      </c>
-      <c r="L298" s="5" t="n">
-        <v>22355</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L298" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N298" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20682,7 +20786,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -20690,31 +20794,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H299" s="5" t="n">
-        <v>13930000</v>
-      </c>
-      <c r="I299" s="5" t="n">
-        <v>27972</v>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K299" s="5" t="n">
-        <v>10447500</v>
-      </c>
-      <c r="L299" s="5" t="n">
-        <v>20979</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L299" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20744,7 +20856,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -20752,31 +20864,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H300" s="5" t="n">
-        <v>16184000</v>
-      </c>
-      <c r="I300" s="5" t="n">
-        <v>30194</v>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K300" s="5" t="n">
-        <v>12138000</v>
-      </c>
-      <c r="L300" s="5" t="n">
-        <v>22646</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20806,7 +20926,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -22290,7 +22410,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -22298,31 +22418,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H323" s="5" t="n">
-        <v>12608000</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>28851</v>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I323" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K323" s="5" t="n">
-        <v>9456000</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>21638</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22352,7 +22480,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -22360,31 +22488,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H324" s="5" t="n">
-        <v>15626000</v>
-      </c>
-      <c r="I324" s="5" t="n">
-        <v>29262</v>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K324" s="5" t="n">
-        <v>11719500</v>
-      </c>
-      <c r="L324" s="5" t="n">
-        <v>21947</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L324" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22550,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -22422,31 +22558,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H325" s="5" t="n">
-        <v>13690000</v>
-      </c>
-      <c r="I325" s="5" t="n">
-        <v>27490</v>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I325" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K325" s="5" t="n">
-        <v>10267500</v>
-      </c>
-      <c r="L325" s="5" t="n">
-        <v>20617</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L325" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M325" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N325" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22620,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -22484,31 +22628,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H326" s="5" t="n">
-        <v>15880000</v>
-      </c>
-      <c r="I326" s="5" t="n">
-        <v>29627</v>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K326" s="5" t="n">
-        <v>11910000</v>
-      </c>
-      <c r="L326" s="5" t="n">
-        <v>22220</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N326" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23264,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -23120,31 +23272,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H336" s="5" t="n">
-        <v>12544000</v>
-      </c>
-      <c r="I336" s="5" t="n">
-        <v>28705</v>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I336" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K336" s="5" t="n">
-        <v>9408000</v>
-      </c>
-      <c r="L336" s="5" t="n">
-        <v>21529</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L336" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N336" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23174,7 +23334,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -23182,31 +23342,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H337" s="5" t="n">
-        <v>15533000</v>
-      </c>
-      <c r="I337" s="5" t="n">
-        <v>29088</v>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I337" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K337" s="5" t="n">
-        <v>11649750</v>
-      </c>
-      <c r="L337" s="5" t="n">
-        <v>21816</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L337" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23236,7 +23404,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -23244,31 +23412,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H338" s="5" t="n">
-        <v>13597000</v>
-      </c>
-      <c r="I338" s="5" t="n">
-        <v>27303</v>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K338" s="5" t="n">
-        <v>10197750</v>
-      </c>
-      <c r="L338" s="5" t="n">
-        <v>20477</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K338" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L338" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N338" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23298,7 +23474,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -23306,31 +23482,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H339" s="5" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="I339" s="5" t="n">
-        <v>29478</v>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I339" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K339" s="5" t="n">
-        <v>11850000</v>
-      </c>
-      <c r="L339" s="5" t="n">
-        <v>22108</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L339" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23360,7 +23544,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -24836,7 +25020,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -24844,31 +25028,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H362" s="5" t="n">
-        <v>12381000</v>
-      </c>
-      <c r="I362" s="5" t="n">
-        <v>28332</v>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I362" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K362" s="5" t="n">
-        <v>9285750</v>
-      </c>
-      <c r="L362" s="5" t="n">
-        <v>21249</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L362" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24898,7 +25090,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -24906,31 +25098,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H363" s="5" t="n">
-        <v>15350000</v>
-      </c>
-      <c r="I363" s="5" t="n">
-        <v>28745</v>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I363" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K363" s="5" t="n">
-        <v>11512500</v>
-      </c>
-      <c r="L363" s="5" t="n">
-        <v>21559</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L363" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M363" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N363" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24960,7 +25160,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -24968,31 +25168,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H364" s="5" t="n">
-        <v>13437000</v>
-      </c>
-      <c r="I364" s="5" t="n">
-        <v>26982</v>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="K364" s="5" t="n">
-        <v>10077750</v>
-      </c>
-      <c r="L364" s="5" t="n">
-        <v>20236</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L364" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25092,7 +25300,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -55425,7 +55633,7 @@
       </c>
       <c r="G802" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H802" s="5" t="n">
@@ -61181,7 +61389,7 @@
       </c>
       <c r="G892" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H892" s="5" t="n">
@@ -65780,38 +65988,30 @@
       </c>
       <c r="F966" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G966" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H966" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I966" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H966" s="5" t="n">
+        <v>11488000</v>
+      </c>
+      <c r="I966" s="5" t="n">
+        <v>23022</v>
       </c>
       <c r="J966" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K966" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L966" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K966" s="5" t="n">
+        <v>11488000</v>
+      </c>
+      <c r="L966" s="5" t="n">
+        <v>23022</v>
       </c>
       <c r="M966" s="3" t="inlineStr">
         <is>
@@ -65820,7 +66020,7 @@
       </c>
       <c r="N966" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -75727,27 +75927,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>210</t>
         </is>
       </c>
     </row>
@@ -76836,36 +77036,36 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -76939,44 +77139,44 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -77050,44 +77250,44 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -77494,12 +77694,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -77605,44 +77805,44 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
-$1676万
-$31,272/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1444万
-$28,990/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1650万
-$30,891/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1332万
-$30,474/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -77716,44 +77916,44 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
-$1666万
-$31,084/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1436万
-$28,829/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1639万
-$30,700/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1324万
-$30,291/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -77827,12 +78027,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -78160,12 +78360,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -78176,28 +78376,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1401万
-$28,133/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1601万
-$29,981/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1292万
-$29,558/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -78271,44 +78471,44 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
-$1618万
-$30,194/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1393万
-$27,972/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1592万
-$29,807/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1285万
-$29,405/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -78501,36 +78701,36 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
-$1588万
-$29,627/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1369万
-$27,490/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1563万
-$29,262/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1261万
-$28,851/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -78604,44 +78804,44 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
-$1580万
-$29,478/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1360万
-$27,303/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1553万
-$29,088/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1254万
-$28,705/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -78826,12 +79026,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -78842,28 +79042,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-$1344万
-$26,982/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
-$1535万
-$28,745/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1238万
-$28,332/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -82096,7 +82296,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="N29" s="23" t="inlineStr"/>
+      <c r="N29" s="24" t="inlineStr"/>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -82184,9 +82384,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L30" s="23" t="inlineStr"/>
-      <c r="M30" s="23" t="inlineStr"/>
-      <c r="N30" s="23" t="inlineStr"/>
+      <c r="L30" s="24" t="inlineStr"/>
+      <c r="M30" s="24" t="inlineStr"/>
+      <c r="N30" s="24" t="inlineStr"/>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -82274,9 +82474,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L31" s="23" t="inlineStr"/>
-      <c r="M31" s="23" t="inlineStr"/>
-      <c r="N31" s="23" t="inlineStr"/>
+      <c r="L31" s="24" t="inlineStr"/>
+      <c r="M31" s="24" t="inlineStr"/>
+      <c r="N31" s="24" t="inlineStr"/>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -82364,9 +82564,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L32" s="23" t="inlineStr"/>
-      <c r="M32" s="23" t="inlineStr"/>
-      <c r="N32" s="23" t="inlineStr"/>
+      <c r="L32" s="24" t="inlineStr"/>
+      <c r="M32" s="24" t="inlineStr"/>
+      <c r="N32" s="24" t="inlineStr"/>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -82438,11 +82638,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J33" s="23" t="inlineStr"/>
-      <c r="K33" s="23" t="inlineStr"/>
-      <c r="L33" s="23" t="inlineStr"/>
-      <c r="M33" s="23" t="inlineStr"/>
-      <c r="N33" s="23" t="inlineStr"/>
+      <c r="J33" s="24" t="inlineStr"/>
+      <c r="K33" s="24" t="inlineStr"/>
+      <c r="L33" s="24" t="inlineStr"/>
+      <c r="M33" s="24" t="inlineStr"/>
+      <c r="N33" s="24" t="inlineStr"/>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
@@ -82514,11 +82714,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr"/>
-      <c r="K34" s="23" t="inlineStr"/>
-      <c r="L34" s="23" t="inlineStr"/>
-      <c r="M34" s="23" t="inlineStr"/>
-      <c r="N34" s="23" t="inlineStr"/>
+      <c r="J34" s="24" t="inlineStr"/>
+      <c r="K34" s="24" t="inlineStr"/>
+      <c r="L34" s="24" t="inlineStr"/>
+      <c r="M34" s="24" t="inlineStr"/>
+      <c r="N34" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -82601,7 +82801,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -82611,7 +82811,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -82743,7 +82943,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $1064万
@@ -82751,7 +82951,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $1061万
@@ -82759,7 +82959,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $1081万
@@ -82767,7 +82967,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J5" s="24" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $1088万
@@ -82775,7 +82975,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
 $1534万
@@ -82783,7 +82983,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>L | 305呎 (1房)
 $1098万
@@ -82791,7 +82991,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M5" s="24" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1602万
@@ -82799,7 +82999,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N5" s="24" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $1038万
@@ -82854,7 +83054,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $1003万
@@ -82862,7 +83062,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $1000万
@@ -82870,7 +83070,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $1020万
@@ -82878,7 +83078,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $1027万
@@ -82886,7 +83086,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
 $1449万
@@ -82894,7 +83094,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>L | 305呎 (1房)
 $1037万
@@ -82902,7 +83102,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1516万
@@ -82910,7 +83110,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $982万
@@ -82965,7 +83165,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $942万
@@ -82973,7 +83173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $938万
@@ -82981,7 +83181,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $959万
@@ -82989,7 +83189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J7" s="24" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $965万
@@ -83013,7 +83213,7 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1430万
@@ -83021,7 +83221,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N7" s="24" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $927万
@@ -83124,7 +83324,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1338万
@@ -83137,7 +83337,7 @@
           <t>N | 278呎 (1房)
 $671万
 $24,129/呎
-(26年-08月-09日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -83258,7 +83458,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 613呎 (2房)
 招标单位
@@ -83266,7 +83466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -83274,7 +83474,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 548呎 (2房)
 招标单位
@@ -83282,7 +83482,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -83615,7 +83815,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 $1410万
@@ -83707,10 +83907,10 @@
           <t>A | 613呎 (2房)
 $1582万
 $25,804/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -84376,7 +84576,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -84392,7 +84592,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -84400,12 +84600,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-招标单位
--
-(在售)</t>
+$1149万
+$23,022/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
@@ -85058,7 +85258,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -85066,7 +85266,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 招标单位
@@ -85399,7 +85599,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 招标单位
@@ -85724,8 +85924,8 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr"/>
-      <c r="F32" s="23" t="inlineStr"/>
+      <c r="E32" s="24" t="inlineStr"/>
+      <c r="F32" s="24" t="inlineStr"/>
       <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
@@ -85782,7 +85982,7 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="N32" s="23" t="inlineStr"/>
+      <c r="N32" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -129,13 +129,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -20150,7 +20150,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -20584,7 +20584,7 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -24710,7 +24710,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -24834,7 +24834,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -75927,12 +75927,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -76851,7 +76851,7 @@
           <t>F | 427呎 (2房)
 $1251万
 $29,288/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -76859,7 +76859,7 @@
           <t>G | 306呎 (1房)
 $858万
 $28,056/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -76867,7 +76867,7 @@
           <t>H | 305呎 (1房)
 $858万
 $28,148/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -76875,10 +76875,10 @@
           <t>J | 305呎 (1房)
 $864万
 $28,328/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K12" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $886万
@@ -76886,7 +76886,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1345万
@@ -76899,7 +76899,7 @@
           <t>M | 481呎 (2房)
 $1530万
 $31,800/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
@@ -76907,7 +76907,7 @@
           <t>N | 288呎 (1房)
 $920万
 $31,951/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -76962,7 +76962,7 @@
           <t>F | 427呎 (2房)
 $1239万
 $29,014/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -76970,7 +76970,7 @@
           <t>G | 306呎 (1房)
 $850万
 $27,768/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -76978,7 +76978,7 @@
           <t>H | 305呎 (1房)
 $850万
 $27,859/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -76986,10 +76986,10 @@
           <t>J | 305呎 (1房)
 $855万
 $28,043/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $877万
@@ -76997,7 +76997,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1331万
@@ -77005,7 +77005,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1514万
@@ -77013,7 +77013,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="N13" s="22" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $911万
@@ -77036,7 +77036,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -77044,7 +77044,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -77052,7 +77052,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -77060,7 +77060,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -77073,7 +77073,7 @@
           <t>F | 427呎 (2房)
 $1227万
 $28,726/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -77081,7 +77081,7 @@
           <t>G | 306呎 (1房)
 $842万
 $27,503/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -77089,7 +77089,7 @@
           <t>H | 305呎 (1房)
 $842万
 $27,593/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -77097,7 +77097,7 @@
           <t>J | 305呎 (1房)
 $847万
 $27,767/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -77105,7 +77105,7 @@
           <t>K | 308呎 (1房)
 $868万
 $28,185/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -77113,10 +77113,10 @@
           <t>L | 430呎 (2房)
 $1318万
 $30,651/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1499万
@@ -77124,7 +77124,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="N14" s="22" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $902万
@@ -77139,7 +77139,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -77147,7 +77147,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -77155,7 +77155,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -77163,7 +77163,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -77171,7 +77171,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -77184,7 +77184,7 @@
           <t>F | 427呎 (2房)
 $1214万
 $28,440/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -77192,7 +77192,7 @@
           <t>G | 306呎 (1房)
 $833万
 $27,222/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -77200,7 +77200,7 @@
           <t>H | 305呎 (1房)
 $833万
 $27,311/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -77208,7 +77208,7 @@
           <t>J | 305呎 (1房)
 $838万
 $27,492/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -77216,7 +77216,7 @@
           <t>K | 308呎 (1房)
 $859万
 $27,903/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -77224,10 +77224,10 @@
           <t>L | 430呎 (2房)
 $1305万
 $30,340/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M15" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1484万
@@ -77235,7 +77235,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="N15" s="22" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $893万
@@ -77250,7 +77250,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -77258,7 +77258,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -77266,7 +77266,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -77274,7 +77274,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -77282,7 +77282,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -77295,7 +77295,7 @@
           <t>F | 427呎 (2房)
 $1202万
 $28,159/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -77303,7 +77303,7 @@
           <t>G | 306呎 (1房)
 $825万
 $26,954/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -77311,7 +77311,7 @@
           <t>H | 305呎 (1房)
 $825万
 $27,043/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -77319,7 +77319,7 @@
           <t>J | 305呎 (1房)
 $830万
 $27,220/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -77346,7 +77346,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="N16" s="22" t="inlineStr">
+      <c r="N16" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $884万
@@ -77406,7 +77406,7 @@
           <t>F | 427呎 (2房)
 $1197万
 $28,028/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -77414,7 +77414,7 @@
           <t>G | 306呎 (1房)
 $821万
 $26,827/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -77422,7 +77422,7 @@
           <t>H | 305呎 (1房)
 $821万
 $26,915/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -77430,7 +77430,7 @@
           <t>J | 305呎 (1房)
 $826万
 $27,082/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -77457,7 +77457,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="N17" s="22" t="inlineStr">
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $879万
@@ -77694,7 +77694,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -77739,7 +77739,7 @@
           <t>F | 427呎 (2房)
 $1178万
 $27,600/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -77747,7 +77747,7 @@
           <t>G | 306呎 (1房)
 $809万
 $26,425/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -77755,7 +77755,7 @@
           <t>H | 305呎 (1房)
 $809万
 $26,511/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -77763,7 +77763,7 @@
           <t>J | 305呎 (1房)
 $814万
 $26,689/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -77771,7 +77771,7 @@
           <t>K | 308呎 (1房)
 $834万
 $27,078/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -77779,7 +77779,7 @@
           <t>L | 430呎 (2房)
 $1266万
 $29,435/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -77787,7 +77787,7 @@
           <t>M | 481呎 (2房)
 $1440万
 $29,938/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -77795,7 +77795,7 @@
           <t>N | 288呎 (1房)
 $863万
 $29,976/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -77805,7 +77805,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -77813,7 +77813,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -77821,7 +77821,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -77829,7 +77829,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -77837,7 +77837,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -77850,7 +77850,7 @@
           <t>F | 427呎 (2房)
 $1167万
 $27,321/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -77858,7 +77858,7 @@
           <t>G | 306呎 (1房)
 $801万
 $26,170/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -77866,7 +77866,7 @@
           <t>H | 305呎 (1房)
 $801万
 $26,256/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -77874,7 +77874,7 @@
           <t>J | 305呎 (1房)
 $806万
 $26,426/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -77882,7 +77882,7 @@
           <t>K | 308呎 (1房)
 $826万
 $26,821/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -77890,7 +77890,7 @@
           <t>L | 430呎 (2房)
 $1253万
 $29,144/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -77898,7 +77898,7 @@
           <t>M | 481呎 (2房)
 $1426万
 $29,638/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -77906,7 +77906,7 @@
           <t>N | 288呎 (1房)
 $853万
 $29,618/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -77916,7 +77916,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -77924,7 +77924,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -77932,7 +77932,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -77940,7 +77940,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -77948,7 +77948,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -77961,7 +77961,7 @@
           <t>F | 427呎 (2房)
 $1161万
 $27,190/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -77969,7 +77969,7 @@
           <t>G | 306呎 (1房)
 $797万
 $26,039/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -77977,7 +77977,7 @@
           <t>H | 305呎 (1房)
 $797万
 $26,125/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -77985,7 +77985,7 @@
           <t>J | 305呎 (1房)
 $802万
 $26,285/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -77993,7 +77993,7 @@
           <t>K | 308呎 (1房)
 $822万
 $26,688/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -78001,7 +78001,7 @@
           <t>L | 430呎 (2房)
 $1247万
 $29,000/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -78009,7 +78009,7 @@
           <t>M | 481呎 (2房)
 $1418万
 $29,489/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -78017,7 +78017,7 @@
           <t>N | 288呎 (1房)
 $848万
 $29,444/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78027,7 +78027,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -78072,7 +78072,7 @@
           <t>F | 427呎 (2房)
 $1156万
 $27,066/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -78080,7 +78080,7 @@
           <t>G | 306呎 (1房)
 $793万
 $25,902/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -78088,7 +78088,7 @@
           <t>H | 305呎 (1房)
 $793万
 $25,987/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -78096,7 +78096,7 @@
           <t>J | 305呎 (1房)
 $798万
 $26,164/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -78104,7 +78104,7 @@
           <t>K | 308呎 (1房)
 $818万
 $26,558/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -78112,7 +78112,7 @@
           <t>L | 430呎 (2房)
 $1240万
 $28,837/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -78120,7 +78120,7 @@
           <t>M | 481呎 (2房)
 $1411万
 $29,341/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -78128,7 +78128,7 @@
           <t>N | 288呎 (1房)
 $843万
 $29,267/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78360,7 +78360,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -78376,7 +78376,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -78384,7 +78384,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -78392,7 +78392,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -78405,7 +78405,7 @@
           <t>F | 427呎 (2房)
 $1138万
 $26,651/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -78413,7 +78413,7 @@
           <t>G | 306呎 (1房)
 $781万
 $25,516/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -78421,7 +78421,7 @@
           <t>H | 305呎 (1房)
 $781万
 $25,600/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -78429,7 +78429,7 @@
           <t>J | 305呎 (1房)
 $786万
 $25,770/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -78437,7 +78437,7 @@
           <t>K | 308呎 (1房)
 $806万
 $26,172/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -78445,7 +78445,7 @@
           <t>L | 430呎 (2房)
 $1222万
 $28,412/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -78453,7 +78453,7 @@
           <t>M | 481呎 (2房)
 $1390万
 $28,890/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -78461,7 +78461,7 @@
           <t>N | 288呎 (1房)
 $829万
 $28,778/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78471,7 +78471,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -78479,7 +78479,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -78487,7 +78487,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -78495,7 +78495,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -78503,7 +78503,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -78516,7 +78516,7 @@
           <t>F | 427呎 (2房)
 $1133万
 $26,534/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -78524,7 +78524,7 @@
           <t>G | 306呎 (1房)
 $777万
 $25,386/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -78532,7 +78532,7 @@
           <t>H | 305呎 (1房)
 $777万
 $25,469/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -78540,7 +78540,7 @@
           <t>J | 305呎 (1房)
 $782万
 $25,643/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -78548,7 +78548,7 @@
           <t>K | 308呎 (1房)
 $802万
 $26,052/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -78556,7 +78556,7 @@
           <t>L | 430呎 (2房)
 $1216万
 $28,272/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -78564,7 +78564,7 @@
           <t>M | 481呎 (2房)
 $1382万
 $28,740/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -78572,7 +78572,7 @@
           <t>N | 288呎 (1房)
 $823万
 $28,573/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78701,7 +78701,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -78709,7 +78709,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -78717,7 +78717,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -78725,7 +78725,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -78738,7 +78738,7 @@
           <t>F | 427呎 (2房)
 $1116万
 $26,131/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -78746,7 +78746,7 @@
           <t>G | 306呎 (1房)
 $766万
 $25,020/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -78754,7 +78754,7 @@
           <t>H | 305呎 (1房)
 $766万
 $25,102/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -78762,7 +78762,7 @@
           <t>J | 305呎 (1房)
 $771万
 $25,266/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -78770,7 +78770,7 @@
           <t>K | 308呎 (1房)
 $790万
 $25,649/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -78786,7 +78786,7 @@
           <t>M | 481呎 (2房)
 $1362万
 $28,310/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N29" s="22" t="inlineStr">
@@ -78794,7 +78794,7 @@
           <t>N | 288呎 (1房)
 $809万
 $28,076/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78804,7 +78804,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -78812,7 +78812,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 536呎 (2房)
 招标单位
@@ -78820,7 +78820,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -78828,7 +78828,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -78836,7 +78836,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -78849,7 +78849,7 @@
           <t>F | 427呎 (2房)
 $1110万
 $26,000/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -78857,7 +78857,7 @@
           <t>G | 306呎 (1房)
 $762万
 $24,902/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -78865,7 +78865,7 @@
           <t>H | 305呎 (1房)
 $762万
 $24,984/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -78873,7 +78873,7 @@
           <t>J | 305呎 (1房)
 $767万
 $25,134/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -78881,7 +78881,7 @@
           <t>K | 308呎 (1房)
 $786万
 $25,519/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -78897,7 +78897,7 @@
           <t>M | 481呎 (2房)
 $1355万
 $28,177/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
@@ -78905,7 +78905,7 @@
           <t>N | 288呎 (1房)
 $804万
 $27,917/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -79026,7 +79026,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
 招标单位
@@ -79042,7 +79042,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
 招标单位
@@ -79050,7 +79050,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 534呎 (2房)
 招标单位
@@ -79058,7 +79058,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
 招标单位
@@ -79071,7 +79071,7 @@
           <t>F | 427呎 (2房)
 $1098万
 $25,724/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -79079,7 +79079,7 @@
           <t>G | 306呎 (1房)
 $747万
 $24,399/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -79087,7 +79087,7 @@
           <t>H | 305呎 (1房)
 $754万
 $24,721/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -79095,7 +79095,7 @@
           <t>J | 305呎 (1房)
 $759万
 $24,895/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -79103,7 +79103,7 @@
           <t>K | 308呎 (1房)
 $778万
 $25,263/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -79111,7 +79111,7 @@
           <t>L | 430呎 (2房)
 $1179万
 $27,428/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -79119,7 +79119,7 @@
           <t>M | 481呎 (2房)
 $1341万
 $27,886/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
@@ -79127,7 +79127,7 @@
           <t>N | 288呎 (1房)
 $794万
 $27,569/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -82943,7 +82943,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $1064万
@@ -82951,7 +82951,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $1061万
@@ -82959,7 +82959,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $1081万
@@ -82967,7 +82967,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $1088万
@@ -82975,7 +82975,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
 $1534万
@@ -82983,7 +82983,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>L | 305呎 (1房)
 $1098万
@@ -82991,7 +82991,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1602万
@@ -82999,7 +82999,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N5" s="23" t="inlineStr">
+      <c r="N5" s="22" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $1038万
@@ -83054,7 +83054,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $1003万
@@ -83062,7 +83062,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $1000万
@@ -83070,7 +83070,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $1020万
@@ -83078,7 +83078,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $1027万
@@ -83086,7 +83086,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>K | 426呎 (2房)
 $1449万
@@ -83094,7 +83094,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>L | 305呎 (1房)
 $1037万
@@ -83102,7 +83102,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1516万
@@ -83110,7 +83110,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N6" s="23" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $982万
@@ -83165,7 +83165,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $942万
@@ -83173,7 +83173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $938万
@@ -83181,7 +83181,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $959万
@@ -83189,7 +83189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $965万
@@ -83213,7 +83213,7 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1430万
@@ -83221,7 +83221,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>N | 278呎 (1房)
 $927万
@@ -83324,7 +83324,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr">
         <is>
           <t>M | 429呎 (2房)
 $1338万
@@ -83458,7 +83458,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 613呎 (2房)
 招标单位
@@ -83466,7 +83466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -83474,7 +83474,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 548呎 (2房)
 招标单位
@@ -83482,7 +83482,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -83815,7 +83815,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 $1410万
@@ -83910,7 +83910,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -84576,7 +84576,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 486呎 (2房)
 招标单位
@@ -84592,7 +84592,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -85258,7 +85258,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
 招标单位
@@ -85266,7 +85266,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 招标单位
@@ -85599,7 +85599,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 招标单位
